--- a/docs/descargapartidasjuridico.xlsx
+++ b/docs/descargapartidasjuridico.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\brandon.mata\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{3DC00BDE-C0C4-414A-91EA-8F480C09BBE2}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{46E249FB-47A5-4DA0-84FF-9C686552A977}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="11505" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -98,7 +98,7 @@
     <t>Corrección de Calidad Extraordinaria</t>
   </si>
   <si>
-    <t>Producción Horas Extra</t>
+    <t>Producción Horas Extras</t>
   </si>
 </sst>
 </file>
@@ -465,7 +465,7 @@
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="15.28515625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="24.7109375" customWidth="1"/>
     <col min="5" max="5" width="10" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="11.85546875" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="10" bestFit="1" customWidth="1"/>
@@ -516,7 +516,7 @@
         <v>2</v>
       </c>
       <c r="D2" t="s">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="E2" t="s">
         <v>12</v>
